--- a/artfynd/A 571-2023 artfynd.xlsx
+++ b/artfynd/A 571-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 571-2023 artfynd.xlsx
+++ b/artfynd/A 571-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107552066</v>
+        <v>107551805</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,23 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580844.8956260292</v>
+        <v>580793</v>
       </c>
       <c r="R2" t="n">
-        <v>6569490.068993117</v>
+        <v>6569464</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hundratals kvadratmeter med lummer i den fuktiga skogsbeklädda mossen.</t>
+          <t>Hackmärken efter nfödoskande spillkråka på tall i mosse.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +787,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogsbeklädd mosse</t>
+          <t>Skogsklädd mosse</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107551663</v>
+        <v>107541915</v>
       </c>
       <c r="B3" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,45 +816,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>102623</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalberget, Ölen, Srm</t>
+          <t>Vitmossen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580778.1025851035</v>
+        <v>580790</v>
       </c>
       <c r="R3" t="n">
-        <v>6569450.285097287</v>
+        <v>6569520</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer i en mosse. Väldiga ytor som täcks av lummer. Avverkningsanmäld.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,19 +906,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Mosse med tall och gran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -939,47 +924,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107551805</v>
+        <v>107551663</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -987,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580793</v>
+        <v>580778</v>
       </c>
       <c r="R4" t="n">
-        <v>6569464</v>
+        <v>6569451</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1037,7 +1017,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hackmärken efter nfödoskande spillkråka på tall i mosse.</t>
+          <t>Växer i en mosse. Väldiga ytor som täcks av lummer. Avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,6 +1026,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1056,7 +1037,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Skogsklädd mosse</t>
+          <t>Mosse med tall och gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,6 +1052,129 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107552066</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dalberget, Ölen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>580845</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6569490</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hundratals kvadratmeter med lummer i den fuktiga skogsbeklädda mossen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsbeklädd mosse</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 571-2023 artfynd.xlsx
+++ b/artfynd/A 571-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107551805</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107541915</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107551663</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1175,8 +1195,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107552066</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>